--- a/finished_data/vector_construction.xlsx
+++ b/finished_data/vector_construction.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="key" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'build'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'index'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'build'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'index'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key'!$A$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,14 +432,9 @@
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,47 +465,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>count_of</t>
+          <t>tokens_in</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>calls</t>
+          <t>tokens_out</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>tries</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tokens_in</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tokens_out</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>seconds_start_to_end</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>seconds_of_calls_added_up</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>seconds_of_the_whole_command</t>
+          <t>seconds</t>
         </is>
       </c>
     </row>
@@ -543,29 +513,18 @@
       <c r="F2" t="n">
         <v>38540</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>records</t>
-        </is>
+      <c r="G2" t="n">
+        <v>4232334</v>
       </c>
       <c r="H2" t="n">
-        <v>38540</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>38540</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4232334</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
         <v>2982.903398909091</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -576,10 +535,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -598,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>records in the index</t>
+          <t>records</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -635,18 +594,8 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>records longer than the model's token limit</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -657,11 +606,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="100" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
@@ -790,12 +739,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How many things the part made or handled. Empty where not counted.</t>
+          <t>Calls to a language model that gave an answer, or requests to an embedding model. Empty where the part made no calls, or where they were not counted.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -812,15 +761,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>count_of</t>
+          <t>tokens_in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What count counts.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Tokens sent to the model. Empty where not counted.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tokens</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -830,17 +783,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calls</t>
+          <t>tokens_out</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Calls to a language model that gave an answer, or requests to an embedding model.</t>
+          <t>Tokens that the model wrote. 0 for an embedding model or an encoder.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>tokens</t>
         </is>
       </c>
     </row>
@@ -852,172 +805,62 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tries</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Every try of those calls, failed tries included. Empty where the tries were not counted.</t>
+          <t>Time of the part, from its start to its end. Empty where not measured.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>seconds</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>index</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tokens_in</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tokens sent to the model.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>tokens</t>
-        </is>
-      </c>
+          <t>What the index holds.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>index</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tokens_out</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tokens that the model wrote. 0 for an embedding model or an encoder.</t>
+          <t>How many.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tokens</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>seconds_start_to_end</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Time from the start to the end of the part. Empty where not measured.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>seconds_of_calls_added_up</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>The time of each call, added up. With several calls at the same time, it is more than seconds_start_to_end. Empty where not measured.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>seconds_of_the_whole_command</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Time of the whole command that made the part, its backup and check included. Empty where not measured.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is counted.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The count.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
           <t>count</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>